--- a/week-01/retail_messy_dataset.xlsx
+++ b/week-01/retail_messy_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\disco\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B433011C-5063-4656-A529-E0EE2FDCFA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94E49A5-51E0-4DB7-896D-ACAD7115F7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Sales Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -739,7 +739,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -770,10 +770,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1756,6 +1755,62 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -3964,7 +4019,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{79D6754B-9F16-4909-8C3D-B2BBB24145C7}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{79D6754B-9F16-4909-8C3D-B2BBB24145C7}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B109:H115" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
@@ -4067,7 +4122,7 @@
   <dataFields count="1">
     <dataField name="Sum of TotalSales" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="6">
     <chartFormat chart="0" format="25" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -4121,6 +4176,18 @@
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="30" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -7197,7 +7264,7 @@
         <v>129</v>
       </c>
       <c r="L67" t="str">
-        <f>PROPER(B67)</f>
+        <f t="shared" ref="L67:L101" si="3">PROPER(B67)</f>
         <v/>
       </c>
       <c r="M67" t="str">
@@ -7234,7 +7301,7 @@
         <v>130</v>
       </c>
       <c r="L68" t="str">
-        <f>PROPER(B68)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M68" t="str">
@@ -7271,7 +7338,7 @@
         <v>131</v>
       </c>
       <c r="L69" t="str">
-        <f>PROPER(B69)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M69" t="str">
@@ -7308,7 +7375,7 @@
         <v>132</v>
       </c>
       <c r="L70" t="str">
-        <f>PROPER(B70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M70" t="str">
@@ -7345,11 +7412,11 @@
         <v>134</v>
       </c>
       <c r="L71" t="str">
-        <f>PROPER(B71)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M71" t="str">
-        <f t="shared" ref="M66:M100" si="3">CLEAN(PROPER(_xlfn.CONCAT(D71,","," ",E71)))</f>
+        <f t="shared" ref="M71:M100" si="4">CLEAN(PROPER(_xlfn.CONCAT(D71,","," ",E71)))</f>
         <v>New York, Ny</v>
       </c>
     </row>
@@ -7382,11 +7449,11 @@
         <v>135</v>
       </c>
       <c r="L72" t="str">
-        <f>PROPER(B72)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>New York, Ny</v>
       </c>
     </row>
@@ -7419,11 +7486,11 @@
         <v>136</v>
       </c>
       <c r="L73" t="str">
-        <f>PROPER(B73)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M73" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Los Angeles, Ca</v>
       </c>
     </row>
@@ -7456,11 +7523,11 @@
         <v>137</v>
       </c>
       <c r="L74" t="str">
-        <f>PROPER(B74)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M74" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -7493,11 +7560,11 @@
         <v>138</v>
       </c>
       <c r="L75" t="str">
-        <f>PROPER(B75)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M75" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Houston, Tx</v>
       </c>
     </row>
@@ -7530,11 +7597,11 @@
         <v>139</v>
       </c>
       <c r="L76" t="str">
-        <f>PROPER(B76)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>New York, Ny</v>
       </c>
     </row>
@@ -7567,11 +7634,11 @@
         <v>141</v>
       </c>
       <c r="L77" t="str">
-        <f>PROPER(B77)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M77" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Houston, Tx</v>
       </c>
     </row>
@@ -7604,11 +7671,11 @@
         <v>142</v>
       </c>
       <c r="L78" t="str">
-        <f>PROPER(B78)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M78" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Diego, Ca</v>
       </c>
     </row>
@@ -7641,11 +7708,11 @@
         <v>143</v>
       </c>
       <c r="L79" t="str">
-        <f>PROPER(B79)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Diego, Ca</v>
       </c>
     </row>
@@ -7678,11 +7745,11 @@
         <v>145</v>
       </c>
       <c r="L80" t="str">
-        <f>PROPER(B80)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M80" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -7715,11 +7782,11 @@
         <v>146</v>
       </c>
       <c r="L81" t="str">
-        <f>PROPER(B81)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M81" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Chicago, Il</v>
       </c>
     </row>
@@ -7752,11 +7819,11 @@
         <v>147</v>
       </c>
       <c r="L82" t="str">
-        <f>PROPER(B82)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M82" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -7789,11 +7856,11 @@
         <v>148</v>
       </c>
       <c r="L83" t="str">
-        <f>PROPER(B83)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M83" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -7826,11 +7893,11 @@
         <v>149</v>
       </c>
       <c r="L84" t="str">
-        <f>PROPER(B84)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M84" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -7863,11 +7930,11 @@
         <v>150</v>
       </c>
       <c r="L85" t="str">
-        <f>PROPER(B85)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M85" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Diego, Ca</v>
       </c>
     </row>
@@ -7900,11 +7967,11 @@
         <v>151</v>
       </c>
       <c r="L86" t="str">
-        <f>PROPER(B86)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Los Angeles, Ca</v>
       </c>
     </row>
@@ -7937,11 +8004,11 @@
         <v>152</v>
       </c>
       <c r="L87" t="str">
-        <f>PROPER(B87)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M87" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Philadelphia, Pa</v>
       </c>
     </row>
@@ -7974,11 +8041,11 @@
         <v>153</v>
       </c>
       <c r="L88" t="str">
-        <f>PROPER(B88)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M88" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Phoenix, Az</v>
       </c>
     </row>
@@ -8011,11 +8078,11 @@
         <v>154</v>
       </c>
       <c r="L89" t="str">
-        <f>PROPER(B89)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M89" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Houston, Tx</v>
       </c>
     </row>
@@ -8048,11 +8115,11 @@
         <v>155</v>
       </c>
       <c r="L90" t="str">
-        <f>PROPER(B90)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M90" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Los Angeles, Ca</v>
       </c>
     </row>
@@ -8085,11 +8152,11 @@
         <v>156</v>
       </c>
       <c r="L91" t="str">
-        <f>PROPER(B91)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M91" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Chicago, Il</v>
       </c>
     </row>
@@ -8122,11 +8189,11 @@
         <v>157</v>
       </c>
       <c r="L92" t="str">
-        <f>PROPER(B92)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M92" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Houston, Tx</v>
       </c>
     </row>
@@ -8159,11 +8226,11 @@
         <v>159</v>
       </c>
       <c r="L93" t="str">
-        <f>PROPER(B93)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M93" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Philadelphia, Pa</v>
       </c>
     </row>
@@ -8196,11 +8263,11 @@
         <v>160</v>
       </c>
       <c r="L94" t="str">
-        <f>PROPER(B94)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Chicago, Il</v>
       </c>
     </row>
@@ -8233,11 +8300,11 @@
         <v>161</v>
       </c>
       <c r="L95" t="str">
-        <f>PROPER(B95)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M95" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>New York, Ny</v>
       </c>
     </row>
@@ -8270,11 +8337,11 @@
         <v>162</v>
       </c>
       <c r="L96" t="str">
-        <f>PROPER(B96)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M96" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Philadelphia, Pa</v>
       </c>
     </row>
@@ -8307,11 +8374,11 @@
         <v>163</v>
       </c>
       <c r="L97" t="str">
-        <f>PROPER(B97)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M97" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Phoenix, Az</v>
       </c>
     </row>
@@ -8344,11 +8411,11 @@
         <v>164</v>
       </c>
       <c r="L98" t="str">
-        <f>PROPER(B98)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M98" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>New York, Ny</v>
       </c>
     </row>
@@ -8381,11 +8448,11 @@
         <v>165</v>
       </c>
       <c r="L99" t="str">
-        <f>PROPER(B99)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M99" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>San Antonio, Tx</v>
       </c>
     </row>
@@ -8418,11 +8485,11 @@
         <v>166</v>
       </c>
       <c r="L100" t="str">
-        <f>PROPER(B100)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M100" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Chicago, Il</v>
       </c>
     </row>
@@ -8455,7 +8522,7 @@
         <v>167</v>
       </c>
       <c r="L101" t="str">
-        <f>PROPER(B101)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M101" t="str">
@@ -8467,15 +8534,15 @@
       <c r="C108" s="1"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C110" t="s">
@@ -8498,117 +8565,117 @@
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111">
         <v>1424</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111">
         <v>22475</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111">
         <v>6279</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111">
         <v>7689</v>
       </c>
-      <c r="G111" s="2">
+      <c r="G111">
         <v>7984</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111">
         <v>45851</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112">
         <v>1869</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112">
         <v>9889</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112">
         <v>2392</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112">
         <v>9786</v>
       </c>
-      <c r="G112" s="2">
+      <c r="G112">
         <v>4990</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112">
         <v>28926</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113">
         <v>2047</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113">
         <v>21576</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113">
         <v>4485</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113">
         <v>9087</v>
       </c>
-      <c r="G113" s="2">
+      <c r="G113">
         <v>9481</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113">
         <v>46676</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114">
         <v>1068</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114">
         <v>24273</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114">
         <v>1794</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114">
         <v>9786</v>
       </c>
-      <c r="G114" s="2">
+      <c r="G114">
         <v>10978</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114">
         <v>47899</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115">
         <v>6408</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115">
         <v>78213</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115">
         <v>14950</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115">
         <v>36348</v>
       </c>
-      <c r="G115" s="2">
+      <c r="G115">
         <v>33433</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115">
         <v>169352</v>
       </c>
     </row>
